--- a/research/traditional_assets/database/data/south_africa/south_africa_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_oil_gas_production_and_exploration.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.346</v>
+        <v>-0.00129</v>
       </c>
       <c r="G2">
-        <v>-15.06410256410256</v>
+        <v>-16.55844155844156</v>
       </c>
       <c r="H2">
-        <v>-15.06410256410256</v>
+        <v>-16.55844155844156</v>
       </c>
       <c r="I2">
-        <v>-16.28205128205128</v>
+        <v>-17.07792207792208</v>
       </c>
       <c r="J2">
-        <v>-16.28205128205128</v>
+        <v>-17.07792207792208</v>
       </c>
       <c r="K2">
-        <v>-2.82</v>
+        <v>-1.94</v>
       </c>
       <c r="L2">
-        <v>-18.07692307692308</v>
+        <v>-12.5974025974026</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.53</v>
+        <v>5.76</v>
       </c>
       <c r="V2">
-        <v>0.01342715861544314</v>
+        <v>0.02923857868020304</v>
       </c>
       <c r="W2">
-        <v>-0.2169230769230769</v>
+        <v>-0.097</v>
       </c>
       <c r="X2">
-        <v>0.1077269734255093</v>
+        <v>0.1943865967489939</v>
       </c>
       <c r="Y2">
-        <v>-0.3246500503485862</v>
+        <v>-0.2913865967489939</v>
       </c>
       <c r="Z2">
-        <v>0.004785276073619633</v>
+        <v>0.002929427430093209</v>
       </c>
       <c r="AA2">
-        <v>-0.07791411042944786</v>
+        <v>-0.05002853338405935</v>
       </c>
       <c r="AB2">
-        <v>0.09937342905640034</v>
+        <v>0.1679104839400164</v>
       </c>
       <c r="AC2">
-        <v>-0.1772875394858482</v>
+        <v>-0.2179390173240758</v>
       </c>
       <c r="AD2">
-        <v>36.1</v>
+        <v>51.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>36.1</v>
+        <v>51.7</v>
       </c>
       <c r="AG2">
-        <v>32.57</v>
+        <v>45.94</v>
       </c>
       <c r="AH2">
-        <v>0.1207357859531773</v>
+        <v>0.207880981101729</v>
       </c>
       <c r="AI2">
-        <v>0.64349376114082</v>
+        <v>0.5881683731513083</v>
       </c>
       <c r="AJ2">
-        <v>0.1102311571394727</v>
+        <v>0.1891001893471639</v>
       </c>
       <c r="AK2">
-        <v>0.6195548792086741</v>
+        <v>0.5592890187484781</v>
       </c>
       <c r="AL2">
-        <v>0.299</v>
+        <v>0.288</v>
       </c>
       <c r="AM2">
-        <v>0.289</v>
+        <v>0.214</v>
       </c>
       <c r="AN2">
-        <v>-15.36170212765957</v>
+        <v>-20.1953125</v>
       </c>
       <c r="AO2">
-        <v>-8.494983277591974</v>
+        <v>-9.131944444444445</v>
       </c>
       <c r="AP2">
-        <v>-13.85957446808511</v>
+        <v>-17.9453125</v>
       </c>
       <c r="AQ2">
-        <v>-8.788927335640139</v>
+        <v>-12.28971962616823</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.346</v>
+        <v>-0.00129</v>
       </c>
       <c r="G3">
-        <v>-15.06410256410256</v>
+        <v>-16.55844155844156</v>
       </c>
       <c r="H3">
-        <v>-15.06410256410256</v>
+        <v>-16.55844155844156</v>
       </c>
       <c r="I3">
-        <v>-16.28205128205128</v>
+        <v>-17.07792207792208</v>
       </c>
       <c r="J3">
-        <v>-16.28205128205128</v>
+        <v>-17.07792207792208</v>
       </c>
       <c r="K3">
-        <v>-2.82</v>
+        <v>-1.94</v>
       </c>
       <c r="L3">
-        <v>-18.07692307692308</v>
+        <v>-12.5974025974026</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.53</v>
+        <v>5.76</v>
       </c>
       <c r="V3">
-        <v>0.01342715861544314</v>
+        <v>0.02923857868020304</v>
       </c>
       <c r="W3">
-        <v>-0.2169230769230769</v>
+        <v>-0.097</v>
       </c>
       <c r="X3">
-        <v>0.1077269734255093</v>
+        <v>0.1943865967489939</v>
       </c>
       <c r="Y3">
-        <v>-0.3246500503485862</v>
+        <v>-0.2913865967489939</v>
       </c>
       <c r="Z3">
-        <v>0.004785276073619633</v>
+        <v>0.002929427430093209</v>
       </c>
       <c r="AA3">
-        <v>-0.07791411042944786</v>
+        <v>-0.05002853338405935</v>
       </c>
       <c r="AB3">
-        <v>0.09937342905640034</v>
+        <v>0.1679104839400164</v>
       </c>
       <c r="AC3">
-        <v>-0.1772875394858482</v>
+        <v>-0.2179390173240758</v>
       </c>
       <c r="AD3">
-        <v>36.1</v>
+        <v>51.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>36.1</v>
+        <v>51.7</v>
       </c>
       <c r="AG3">
-        <v>32.57</v>
+        <v>45.94</v>
       </c>
       <c r="AH3">
-        <v>0.1207357859531773</v>
+        <v>0.207880981101729</v>
       </c>
       <c r="AI3">
-        <v>0.64349376114082</v>
+        <v>0.5881683731513083</v>
       </c>
       <c r="AJ3">
-        <v>0.1102311571394727</v>
+        <v>0.1891001893471639</v>
       </c>
       <c r="AK3">
-        <v>0.6195548792086741</v>
+        <v>0.5592890187484781</v>
       </c>
       <c r="AL3">
-        <v>0.299</v>
+        <v>0.288</v>
       </c>
       <c r="AM3">
-        <v>0.289</v>
+        <v>0.214</v>
       </c>
       <c r="AN3">
-        <v>-15.36170212765957</v>
+        <v>-20.1953125</v>
       </c>
       <c r="AO3">
-        <v>-8.494983277591974</v>
+        <v>-9.131944444444445</v>
       </c>
       <c r="AP3">
-        <v>-13.85957446808511</v>
+        <v>-17.9453125</v>
       </c>
       <c r="AQ3">
-        <v>-8.788927335640139</v>
+        <v>-12.28971962616823</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_africa/south_africa_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_oil_gas_production_and_exploration.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00129</v>
+        <v>0.615</v>
       </c>
       <c r="G2">
-        <v>-16.55844155844156</v>
+        <v>-1.231182795698925</v>
       </c>
       <c r="H2">
-        <v>-16.55844155844156</v>
+        <v>-1.231182795698925</v>
       </c>
       <c r="I2">
-        <v>-17.07792207792208</v>
+        <v>-1.854838709677419</v>
       </c>
       <c r="J2">
-        <v>-17.07792207792208</v>
+        <v>-1.854838709677419</v>
       </c>
       <c r="K2">
-        <v>-1.94</v>
+        <v>-2.42</v>
       </c>
       <c r="L2">
-        <v>-12.5974025974026</v>
+        <v>-1.301075268817204</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.76</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="V2">
-        <v>0.02923857868020304</v>
+        <v>0.07796208530805687</v>
       </c>
       <c r="W2">
-        <v>-0.097</v>
+        <v>-0.06685082872928176</v>
       </c>
       <c r="X2">
-        <v>0.1943865967489939</v>
+        <v>0.1583129613411454</v>
       </c>
       <c r="Y2">
-        <v>-0.2913865967489939</v>
+        <v>-0.2251637900704271</v>
       </c>
       <c r="Z2">
-        <v>0.002929427430093209</v>
+        <v>0.02264426588750913</v>
       </c>
       <c r="AA2">
-        <v>-0.05002853338405935</v>
+        <v>-0.04200146092037984</v>
       </c>
       <c r="AB2">
-        <v>0.1679104839400164</v>
+        <v>0.124984050091093</v>
       </c>
       <c r="AC2">
-        <v>-0.2179390173240758</v>
+        <v>-0.1669855110114729</v>
       </c>
       <c r="AD2">
-        <v>51.7</v>
+        <v>66</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>51.7</v>
+        <v>66</v>
       </c>
       <c r="AG2">
-        <v>45.94</v>
+        <v>56.13</v>
       </c>
       <c r="AH2">
-        <v>0.207880981101729</v>
+        <v>0.3426791277258567</v>
       </c>
       <c r="AI2">
-        <v>0.5881683731513083</v>
+        <v>0.5994550408719347</v>
       </c>
       <c r="AJ2">
-        <v>0.1891001893471639</v>
+        <v>0.3071745197832869</v>
       </c>
       <c r="AK2">
-        <v>0.5592890187484781</v>
+        <v>0.5600119724633343</v>
       </c>
       <c r="AL2">
-        <v>0.288</v>
+        <v>0.574</v>
       </c>
       <c r="AM2">
-        <v>0.214</v>
+        <v>0.1749999999999999</v>
       </c>
       <c r="AN2">
-        <v>-20.1953125</v>
+        <v>-21.49837133550489</v>
       </c>
       <c r="AO2">
-        <v>-9.131944444444445</v>
+        <v>-6.010452961672475</v>
       </c>
       <c r="AP2">
-        <v>-17.9453125</v>
+        <v>-18.28338762214984</v>
       </c>
       <c r="AQ2">
-        <v>-12.28971962616823</v>
+        <v>-19.71428571428572</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00129</v>
+        <v>0.615</v>
       </c>
       <c r="G3">
-        <v>-16.55844155844156</v>
+        <v>-1.231182795698925</v>
       </c>
       <c r="H3">
-        <v>-16.55844155844156</v>
+        <v>-1.231182795698925</v>
       </c>
       <c r="I3">
-        <v>-17.07792207792208</v>
+        <v>-1.854838709677419</v>
       </c>
       <c r="J3">
-        <v>-17.07792207792208</v>
+        <v>-1.854838709677419</v>
       </c>
       <c r="K3">
-        <v>-1.94</v>
+        <v>-2.42</v>
       </c>
       <c r="L3">
-        <v>-12.5974025974026</v>
+        <v>-1.301075268817204</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.76</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="V3">
-        <v>0.02923857868020304</v>
+        <v>0.07796208530805687</v>
       </c>
       <c r="W3">
-        <v>-0.097</v>
+        <v>-0.06685082872928176</v>
       </c>
       <c r="X3">
-        <v>0.1943865967489939</v>
+        <v>0.1583129613411454</v>
       </c>
       <c r="Y3">
-        <v>-0.2913865967489939</v>
+        <v>-0.2251637900704271</v>
       </c>
       <c r="Z3">
-        <v>0.002929427430093209</v>
+        <v>0.02264426588750913</v>
       </c>
       <c r="AA3">
-        <v>-0.05002853338405935</v>
+        <v>-0.04200146092037984</v>
       </c>
       <c r="AB3">
-        <v>0.1679104839400164</v>
+        <v>0.124984050091093</v>
       </c>
       <c r="AC3">
-        <v>-0.2179390173240758</v>
+        <v>-0.1669855110114729</v>
       </c>
       <c r="AD3">
-        <v>51.7</v>
+        <v>66</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>51.7</v>
+        <v>66</v>
       </c>
       <c r="AG3">
-        <v>45.94</v>
+        <v>56.13</v>
       </c>
       <c r="AH3">
-        <v>0.207880981101729</v>
+        <v>0.3426791277258567</v>
       </c>
       <c r="AI3">
-        <v>0.5881683731513083</v>
+        <v>0.5994550408719347</v>
       </c>
       <c r="AJ3">
-        <v>0.1891001893471639</v>
+        <v>0.3071745197832869</v>
       </c>
       <c r="AK3">
-        <v>0.5592890187484781</v>
+        <v>0.5600119724633343</v>
       </c>
       <c r="AL3">
-        <v>0.288</v>
+        <v>0.574</v>
       </c>
       <c r="AM3">
-        <v>0.214</v>
+        <v>0.1749999999999999</v>
       </c>
       <c r="AN3">
-        <v>-20.1953125</v>
+        <v>-21.49837133550489</v>
       </c>
       <c r="AO3">
-        <v>-9.131944444444445</v>
+        <v>-6.010452961672475</v>
       </c>
       <c r="AP3">
-        <v>-17.9453125</v>
+        <v>-18.28338762214984</v>
       </c>
       <c r="AQ3">
-        <v>-12.28971962616823</v>
+        <v>-19.71428571428572</v>
       </c>
     </row>
   </sheetData>
